--- a/effects.xlsx
+++ b/effects.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:I54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,10 +407,25 @@
         <v>Effect Type_x000d_</v>
       </c>
       <c r="C1" t="str">
+        <v>Growth</v>
+      </c>
+      <c r="D1" t="str">
         <v>Short Description</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Long Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Amount Type</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Duration</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Target</v>
       </c>
     </row>
     <row r="2">
@@ -421,10 +436,22 @@
         <v>Active</v>
       </c>
       <c r="C2" t="str">
+        <v>-</v>
+      </c>
+      <c r="D2" t="str">
         <v>When used, reduce your Max HP by X</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>Each time this attack is used, reduces attackers max HP by X.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>5</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Number</v>
+      </c>
+      <c r="I2" t="str">
+        <v>self</v>
       </c>
     </row>
     <row r="3">
@@ -435,26 +462,48 @@
         <v>Active</v>
       </c>
       <c r="C3" t="str">
+        <v>+</v>
+      </c>
+      <c r="D3" t="str">
         <v>Increase damage based on shield</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>Gets +X% attack power per shield that the entity has</v>
       </c>
-    </row>
-    <row r="4" xml:space="preserve">
+      <c r="F3" t="str">
+        <v>5</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Percent</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="str">
         <v>soak</v>
       </c>
       <c r="B4" t="str">
         <v>Stack</v>
       </c>
-      <c r="C4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Increase LIGHTNING damage
-Decrease FIRE damage</v>
-      </c>
-      <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Increase LIGHTNING damage taken by X% per stack 
-Decrease FIRE damage taken by X% per stack</v>
+      <c r="C4" t="str">
+        <v>+</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Applies SOAK stacks</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Applies X SOAK stack(s) on hit</v>
+      </c>
+      <c r="F4" t="str">
+        <v>1</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Number</v>
+      </c>
+      <c r="H4" t="str">
+        <v>3</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -465,39 +514,75 @@
         <v>Active</v>
       </c>
       <c r="C5" t="str">
+        <v>+</v>
+      </c>
+      <c r="D5" t="str">
         <v>Increase power when used consecutively</v>
       </c>
-      <c r="D5" t="str" xml:space="preserve">
+      <c r="E5" t="str" xml:space="preserve">
         <v xml:space="preserve">If your next attack is this attack, it deals X% additional damage. 
 Can stack, but does not carry over across turns</v>
       </c>
+      <c r="F5" t="str">
+        <v>50</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Percent</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>burn_x000d_</v>
+        <v>burn</v>
       </c>
       <c r="B6" t="str">
         <v>Stack</v>
       </c>
       <c r="C6" t="str">
-        <v>Increase fire damage</v>
+        <v>+</v>
       </c>
       <c r="D6" t="str">
-        <v>Gives +X% fire damage per stack.</v>
+        <v>Applies BURN stacks</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Applies X BURN stack(s) on hit</v>
+      </c>
+      <c r="F6" t="str">
+        <v>1</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Number</v>
+      </c>
+      <c r="H6" t="str">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>thorns_x000d_</v>
+        <v>thorns</v>
       </c>
       <c r="B7" t="str">
         <v>Stack</v>
       </c>
       <c r="C7" t="str">
-        <v>Deals damage when attacked</v>
+        <v>+</v>
       </c>
       <c r="D7" t="str">
-        <v>When attacked, deals X% of attackers damage per stack back to them</v>
+        <v>Applies THORN stacks to self</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Applies X THORNS stack(s) on self when used</v>
+      </c>
+      <c r="F7" t="str">
+        <v>1</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Number</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2</v>
+      </c>
+      <c r="I7" t="str">
+        <v>self</v>
       </c>
     </row>
     <row r="8">
@@ -508,10 +593,19 @@
         <v>Active</v>
       </c>
       <c r="C8" t="str">
+        <v>+</v>
+      </c>
+      <c r="D8" t="str">
         <v>If next attack is ELEMENT, it deals more damage</v>
       </c>
-      <c r="D8" t="str">
-        <v>Next attack deals X% more damage if it is the associated type</v>
+      <c r="E8" t="str">
+        <v>Your next attack deals +X% more damage if it is the associated type</v>
+      </c>
+      <c r="F8" t="str">
+        <v>50</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -521,55 +615,97 @@
       <c r="B9" t="str">
         <v>Passive</v>
       </c>
-      <c r="C9" t="str" xml:space="preserve">
+      <c r="C9" t="str">
+        <v>+</v>
+      </c>
+      <c r="D9" t="str" xml:space="preserve">
         <v xml:space="preserve">Increase LIGHTNING Damage
 Decrease EARTH damage</v>
       </c>
-      <c r="D9" t="str" xml:space="preserve">
+      <c r="E9" t="str" xml:space="preserve">
         <v xml:space="preserve">Reduce EARTH damage taken by X%
 Increase LIGHTNING damage taken by X%</v>
       </c>
+      <c r="F9" t="str">
+        <v>50</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Percent</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>rage_x000d_</v>
+        <v>rage</v>
       </c>
       <c r="B10" t="str">
         <v>Active</v>
       </c>
       <c r="C10" t="str">
-        <v>Deals more damage the closer you are to death</v>
+        <v>+</v>
       </c>
       <c r="D10" t="str">
-        <v>The lower the players health, the more this attack does</v>
+        <v>The lower your health, the higher the damage</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Increase damage by X for every 1 health missing</v>
+      </c>
+      <c r="F10" t="str">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Number</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>energize_x000d_</v>
+        <v>energize</v>
       </c>
       <c r="B11" t="str">
         <v>Stack</v>
       </c>
       <c r="C11" t="str">
+        <v>=</v>
+      </c>
+      <c r="D11" t="str">
         <v>Start you next turn with more energy</v>
       </c>
-      <c r="D11" t="str">
+      <c r="E11" t="str">
         <v>Each stack provides +X energy at the start of your next turn!</v>
+      </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Number</v>
+      </c>
+      <c r="H11" t="str">
+        <v>2</v>
+      </c>
+      <c r="I11" t="str">
+        <v>self</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>heal_x000d_</v>
+        <v>heal</v>
       </c>
       <c r="B12" t="str">
         <v>Active</v>
       </c>
       <c r="C12" t="str">
-        <v>Restores HP</v>
+        <v>+</v>
       </c>
       <c r="D12" t="str">
         <v>Restores HP</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Restores X HP</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Number</v>
       </c>
     </row>
     <row r="13">
@@ -580,10 +716,22 @@
         <v>Active</v>
       </c>
       <c r="C13" t="str">
-        <v>If next attack is ELEMENT, it costs less energy</v>
+        <v>+</v>
       </c>
       <c r="D13" t="str">
+        <v>If next attack is the same element, it costs less energy</v>
+      </c>
+      <c r="E13" t="str">
         <v>Next attack costs X less energy if it is the associated type</v>
+      </c>
+      <c r="F13" t="str">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Number</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -594,42 +742,71 @@
         <v>Active</v>
       </c>
       <c r="C14" t="str">
-        <v>On use, deal damage to yourself</v>
+        <v>-</v>
       </c>
       <c r="D14" t="str">
+        <v>On use, deal damage to self</v>
+      </c>
+      <c r="E14" t="str">
         <v>When attacking, deals X% of the damage to yourself</v>
       </c>
-    </row>
-    <row r="15" xml:space="preserve">
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Percent</v>
+      </c>
+      <c r="I14" t="str">
+        <v>self</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="str">
-        <v>charge_x000d_</v>
+        <v>charge</v>
       </c>
       <c r="B15" t="str">
         <v>Active</v>
       </c>
       <c r="C15" t="str">
-        <v>Consume energy for increase damage next turn</v>
-      </c>
-      <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Consumes ALL energy. 
-Next turn, deals an additional X% damage per energy consumed</v>
+        <v>+</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Increase damage based on energy cost</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Deals +X% more damage for each energy in its cost</v>
+      </c>
+      <c r="F15" t="str">
+        <v>50</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>shield_x000d_</v>
+        <v>shield</v>
       </c>
       <c r="B16" t="str">
         <v>Active</v>
       </c>
       <c r="C16" t="str">
-        <v>Absorbs incoming damage</v>
+        <v>=</v>
       </c>
       <c r="D16" t="str">
         <v>Absorbs incoming damage</v>
       </c>
-    </row>
-    <row r="17" xml:space="preserve">
+      <c r="E16" t="str">
+        <v>Absorbs X damage per 1 shield</v>
+      </c>
+      <c r="F16" t="str">
+        <v>1</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Number</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="str">
         <v>freeze</v>
       </c>
@@ -637,116 +814,298 @@
         <v>Stack</v>
       </c>
       <c r="C17" t="str">
-        <v>Significantly increase fire damage</v>
-      </c>
-      <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Increase FIRE damage by X% per stack. 
-Removes all stacks from entity when they are hit with a fire attack</v>
+        <v>=</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Transform SOAK stacks into ICE stacks</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Transforms X% of SOAK stacks into ICE stacks</v>
+      </c>
+      <c r="F17" t="str">
+        <v>100</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Percent</v>
+      </c>
+      <c r="H17" t="str">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Powerful</v>
+        <v>exponential</v>
       </c>
       <c r="B18" t="str">
-        <v>Passive</v>
+        <v>Active</v>
       </c>
       <c r="C18" t="str">
-        <v>Increase damage by 150%</v>
+        <v>+</v>
       </c>
       <c r="D18" t="str">
-        <v>Increase damage by 150%</v>
+        <v>Permanently increase damage on use</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Each time this attack is used, permanently increase its damage by X%</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Exponential</v>
+        <v>resistant</v>
       </c>
       <c r="B19" t="str">
-        <v>Active</v>
+        <v>Passive</v>
       </c>
       <c r="C19" t="str">
-        <v>Permanently increase damage on use</v>
+        <v>+</v>
       </c>
       <c r="D19" t="str">
-        <v>Each time this attack is used, permanently increase its damage by X%</v>
+        <v>Reduce ELEMENT damage</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Reduce ELEMENT damage received by X%</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Resistant</v>
+        <v>vulnerable</v>
       </c>
       <c r="B20" t="str">
         <v>Passive</v>
       </c>
       <c r="C20" t="str">
-        <v>Reduce ELEMENT damage</v>
+        <v>-</v>
       </c>
       <c r="D20" t="str">
-        <v>Reduce ELEMENT damage taken by X%</v>
+        <v>Increase ELEMENT damage</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Increase ELEMENT damage received by X%</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Vulnerable</v>
+        <v>squishy</v>
       </c>
       <c r="B21" t="str">
-        <v>Passive</v>
+        <v>Active</v>
       </c>
       <c r="C21" t="str">
-        <v>Increase ELEMENT damage</v>
+        <v>-</v>
       </c>
       <c r="D21" t="str">
-        <v>Increase ELEMENT damage taken by X%</v>
+        <v>Removes X% shield</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Removes X% of shield from attacker when used</v>
+      </c>
+      <c r="F21" t="str">
+        <v>100</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Squishy</v>
+        <v>multihit</v>
       </c>
       <c r="B22" t="str">
         <v>Active</v>
       </c>
       <c r="C22" t="str">
-        <v>Removes ALL shield</v>
+        <v>+</v>
       </c>
       <c r="D22" t="str">
-        <v>Removes ALL shield from attacker when used</v>
+        <v>Hits multiple times</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Triggers X times on use</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Number</v>
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="str">
+        <v>exhaust</v>
+      </c>
       <c r="B23" t="str">
-        <v>_x000d_</v>
+        <v>Active</v>
+      </c>
+      <c r="C23" t="str">
+        <v>-</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Remove X% of energy on use</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Removes X% of energy when used</v>
+      </c>
+      <c r="F23" t="str">
+        <v>100</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="str">
+        <v>powerful</v>
+      </c>
       <c r="B24" t="str">
-        <v>_x000d_</v>
+        <v>Creation</v>
+      </c>
+      <c r="C24" t="str">
+        <v>+</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Enhances damage</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Increase damage by X% on creation</v>
+      </c>
+      <c r="F24" t="str">
+        <v>250</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="str">
+        <v>energetic</v>
+      </c>
       <c r="B25" t="str">
-        <v>_x000d_</v>
+        <v>Creation</v>
+      </c>
+      <c r="C25" t="str">
+        <v>+</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Decreases energy cost</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Decrease energy cost by X on creation</v>
+      </c>
+      <c r="F25" t="str">
+        <v>1</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Number</v>
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="str">
+        <v>efficient</v>
+      </c>
       <c r="B26" t="str">
-        <v>_x000d_</v>
+        <v>Creation</v>
+      </c>
+      <c r="C26" t="str">
+        <v>+</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Enhances effects</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Increases value of effect by X% on creation</v>
+      </c>
+      <c r="F26" t="str">
+        <v>150</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="str">
+        <v>boosted</v>
+      </c>
       <c r="B27" t="str">
-        <v>_x000d_</v>
+        <v>Passive</v>
+      </c>
+      <c r="C27" t="str">
+        <v>+</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Increases energy at turn start</v>
+      </c>
+      <c r="E27" t="str">
+        <v>+X energy at turn start</v>
+      </c>
+      <c r="F27" t="str">
+        <v>1</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Number</v>
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="str">
+        <v>healthy</v>
+      </c>
       <c r="B28" t="str">
-        <v>_x000d_</v>
+        <v>Passive</v>
+      </c>
+      <c r="C28" t="str">
+        <v>+</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Increases Max HP</v>
+      </c>
+      <c r="E28" t="str">
+        <v>+X Max HP</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Number</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="str">
+        <v>brittle</v>
+      </c>
       <c r="B29" t="str">
-        <v>_x000d_</v>
+        <v>Element</v>
+      </c>
+      <c r="C29" t="str">
+        <v>+</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Consumed after X uses in a FORMULA</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Consumed after X uses in a FORMULA</v>
+      </c>
+      <c r="F29" t="str">
+        <v>1</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Number</v>
       </c>
     </row>
     <row r="30">
@@ -876,7 +1235,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/effects.xlsx
+++ b/effects.xlsx
@@ -397,34 +397,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:J34"/>
+  <cols>
+    <col min="1" max="1" width="42.00390625" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="42.00390625" customWidth="1"/>
+    <col min="4" max="4" width="42.00390625" customWidth="1"/>
+    <col min="5" max="5" width="50.00390625" customWidth="1"/>
+    <col min="6" max="6" width="50.00390625" customWidth="1"/>
+    <col min="7" max="7" width="42.00390625" customWidth="1"/>
+    <col min="8" max="8" width="42.00390625" customWidth="1"/>
+    <col min="9" max="9" width="42.00390625" customWidth="1"/>
+    <col min="10" max="10" width="42.00390625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Effect</v>
       </c>
       <c r="B1" t="str">
-        <v>Effect Type_x000d_</v>
+        <v>Type</v>
       </c>
       <c r="C1" t="str">
+        <v>Effect Type</v>
+      </c>
+      <c r="D1" t="str">
         <v>Growth</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Short Description</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Long Description</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Amount</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Amount Type</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Duration</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Target</v>
       </c>
     </row>
@@ -433,24 +464,27 @@
         <v>consume</v>
       </c>
       <c r="B2" t="str">
-        <v>Active</v>
+        <v>Fire</v>
       </c>
       <c r="C2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D2" t="str">
         <v>-</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>When used, reduce your Max HP by X</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>Each time this attack is used, reduces attackers max HP by X.</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>5</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Number</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>self</v>
       </c>
     </row>
@@ -459,50 +493,53 @@
         <v>hardened</v>
       </c>
       <c r="B3" t="str">
-        <v>Active</v>
+        <v>Earth</v>
       </c>
       <c r="C3" t="str">
-        <v>+</v>
+        <v>Active</v>
       </c>
       <c r="D3" t="str">
+        <v>+</v>
+      </c>
+      <c r="E3" t="str">
         <v>Increase damage based on shield</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Gets +X% attack power per shield that the entity has</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>5</v>
       </c>
-      <c r="G3" t="str">
-        <v>Percent</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
+      <c r="H3" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>soak</v>
+        <v>soaker</v>
       </c>
       <c r="B4" t="str">
+        <v>Water</v>
+      </c>
+      <c r="C4" t="str">
         <v>Stack</v>
       </c>
-      <c r="C4" t="str">
-        <v>+</v>
-      </c>
       <c r="D4" t="str">
+        <v>+</v>
+      </c>
+      <c r="E4" t="str">
         <v>Applies SOAK stacks</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Applies X SOAK stack(s) on hit</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>1</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Number</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>3</v>
       </c>
     </row>
@@ -511,22 +548,25 @@
         <v>follow up</v>
       </c>
       <c r="B5" t="str">
-        <v>Active</v>
+        <v>Air</v>
       </c>
       <c r="C5" t="str">
-        <v>+</v>
+        <v>Active</v>
       </c>
       <c r="D5" t="str">
+        <v>+</v>
+      </c>
+      <c r="E5" t="str">
         <v>Increase power when used consecutively</v>
       </c>
-      <c r="E5" t="str" xml:space="preserve">
+      <c r="F5" t="str" xml:space="preserve">
         <v xml:space="preserve">If your next attack is this attack, it deals X% additional damage. 
 Can stack, but does not carry over across turns</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>50</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -535,24 +575,27 @@
         <v>burn</v>
       </c>
       <c r="B6" t="str">
+        <v>Fire</v>
+      </c>
+      <c r="C6" t="str">
         <v>Stack</v>
       </c>
-      <c r="C6" t="str">
-        <v>+</v>
-      </c>
       <c r="D6" t="str">
+        <v>+</v>
+      </c>
+      <c r="E6" t="str">
         <v>Applies BURN stacks</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>Applies X BURN stack(s) on hit</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>1</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Number</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>3</v>
       </c>
     </row>
@@ -561,50 +604,56 @@
         <v>thorns</v>
       </c>
       <c r="B7" t="str">
+        <v>Earth</v>
+      </c>
+      <c r="C7" t="str">
         <v>Stack</v>
       </c>
-      <c r="C7" t="str">
-        <v>+</v>
-      </c>
       <c r="D7" t="str">
+        <v>+</v>
+      </c>
+      <c r="E7" t="str">
         <v>Applies THORN stacks to self</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>Applies X THORNS stack(s) on self when used</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>1</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Number</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>2</v>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <v>self</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>power combo_x000d_</v>
+        <v xml:space="preserve">power combo </v>
       </c>
       <c r="B8" t="str">
-        <v>Active</v>
+        <v>Water</v>
       </c>
       <c r="C8" t="str">
-        <v>+</v>
+        <v>Active</v>
       </c>
       <c r="D8" t="str">
+        <v>+</v>
+      </c>
+      <c r="E8" t="str">
         <v>If next attack is ELEMENT, it deals more damage</v>
       </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
         <v>Your next attack deals +X% more damage if it is the associated type</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
         <v>50</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -613,23 +662,26 @@
         <v>float</v>
       </c>
       <c r="B9" t="str">
+        <v>Air</v>
+      </c>
+      <c r="C9" t="str">
         <v>Passive</v>
       </c>
-      <c r="C9" t="str">
-        <v>+</v>
-      </c>
-      <c r="D9" t="str" xml:space="preserve">
+      <c r="D9" t="str">
+        <v>+</v>
+      </c>
+      <c r="E9" t="str" xml:space="preserve">
         <v xml:space="preserve">Increase LIGHTNING Damage
 Decrease EARTH damage</v>
       </c>
-      <c r="E9" t="str" xml:space="preserve">
+      <c r="F9" t="str" xml:space="preserve">
         <v xml:space="preserve">Reduce EARTH damage taken by X%
 Increase LIGHTNING damage taken by X%</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>50</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -638,21 +690,24 @@
         <v>rage</v>
       </c>
       <c r="B10" t="str">
-        <v>Active</v>
+        <v>Fire</v>
       </c>
       <c r="C10" t="str">
-        <v>+</v>
+        <v>Active</v>
       </c>
       <c r="D10" t="str">
+        <v>+</v>
+      </c>
+      <c r="E10" t="str">
         <v>The lower your health, the higher the damage</v>
       </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
         <v>Increase damage by X for every 1 health missing</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>1</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Number</v>
       </c>
     </row>
@@ -661,27 +716,30 @@
         <v>energize</v>
       </c>
       <c r="B11" t="str">
+        <v>Earth</v>
+      </c>
+      <c r="C11" t="str">
         <v>Stack</v>
       </c>
-      <c r="C11" t="str">
+      <c r="D11" t="str">
         <v>=</v>
       </c>
-      <c r="D11" t="str">
+      <c r="E11" t="str">
         <v>Start you next turn with more energy</v>
       </c>
-      <c r="E11" t="str">
+      <c r="F11" t="str">
         <v>Each stack provides +X energy at the start of your next turn!</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>1</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Number</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>2</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <v>self</v>
       </c>
     </row>
@@ -690,21 +748,24 @@
         <v>heal</v>
       </c>
       <c r="B12" t="str">
-        <v>Active</v>
+        <v>Water</v>
       </c>
       <c r="C12" t="str">
-        <v>+</v>
+        <v>Active</v>
       </c>
       <c r="D12" t="str">
+        <v>+</v>
+      </c>
+      <c r="E12" t="str">
         <v>Restores HP</v>
       </c>
-      <c r="E12" t="str">
+      <c r="F12" t="str">
         <v>Restores X HP</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <v>5</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>Number</v>
       </c>
     </row>
@@ -713,25 +774,25 @@
         <v>energy combo</v>
       </c>
       <c r="B13" t="str">
-        <v>Active</v>
+        <v>Air</v>
       </c>
       <c r="C13" t="str">
-        <v>+</v>
+        <v>Active</v>
       </c>
       <c r="D13" t="str">
+        <v>+</v>
+      </c>
+      <c r="E13" t="str">
         <v>If next attack is the same element, it costs less energy</v>
       </c>
-      <c r="E13" t="str">
+      <c r="F13" t="str">
         <v>Next attack costs X less energy if it is the associated type</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
         <v>1</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>Number</v>
-      </c>
-      <c r="I13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -739,24 +800,27 @@
         <v>combust</v>
       </c>
       <c r="B14" t="str">
-        <v>Active</v>
+        <v>Fire</v>
       </c>
       <c r="C14" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D14" t="str">
         <v>-</v>
       </c>
-      <c r="D14" t="str">
+      <c r="E14" t="str">
         <v>On use, deal damage to self</v>
       </c>
-      <c r="E14" t="str">
+      <c r="F14" t="str">
         <v>When attacking, deals X% of the damage to yourself</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>10</v>
       </c>
-      <c r="G14" t="str">
-        <v>Percent</v>
-      </c>
-      <c r="I14" t="str">
+      <c r="H14" t="str">
+        <v>Percent</v>
+      </c>
+      <c r="J14" t="str">
         <v>self</v>
       </c>
     </row>
@@ -765,21 +829,24 @@
         <v>charge</v>
       </c>
       <c r="B15" t="str">
-        <v>Active</v>
+        <v>Earth</v>
       </c>
       <c r="C15" t="str">
-        <v>+</v>
+        <v>Active</v>
       </c>
       <c r="D15" t="str">
+        <v>+</v>
+      </c>
+      <c r="E15" t="str">
         <v>Increase damage based on energy cost</v>
       </c>
-      <c r="E15" t="str">
+      <c r="F15" t="str">
         <v>Deals +X% more damage for each energy in its cost</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>50</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -788,21 +855,24 @@
         <v>shield</v>
       </c>
       <c r="B16" t="str">
-        <v>Active</v>
+        <v>Water, Earth</v>
       </c>
       <c r="C16" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D16" t="str">
         <v>=</v>
       </c>
-      <c r="D16" t="str">
+      <c r="E16" t="str">
         <v>Absorbs incoming damage</v>
       </c>
-      <c r="E16" t="str">
+      <c r="F16" t="str">
         <v>Absorbs X damage per 1 shield</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>1</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>Number</v>
       </c>
     </row>
@@ -811,24 +881,27 @@
         <v>freeze</v>
       </c>
       <c r="B17" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="C17" t="str">
         <v>Stack</v>
       </c>
-      <c r="C17" t="str">
+      <c r="D17" t="str">
         <v>=</v>
       </c>
-      <c r="D17" t="str">
+      <c r="E17" t="str">
         <v>Transform SOAK stacks into ICE stacks</v>
       </c>
-      <c r="E17" t="str">
+      <c r="F17" t="str">
         <v>Transforms X% of SOAK stacks into ICE stacks</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>100</v>
       </c>
-      <c r="G17" t="str">
-        <v>Percent</v>
-      </c>
       <c r="H17" t="str">
+        <v>Percent</v>
+      </c>
+      <c r="I17" t="str">
         <v>1</v>
       </c>
     </row>
@@ -837,21 +910,24 @@
         <v>exponential</v>
       </c>
       <c r="B18" t="str">
-        <v>Active</v>
+        <v>Fire, Earth</v>
       </c>
       <c r="C18" t="str">
-        <v>+</v>
+        <v>Active</v>
       </c>
       <c r="D18" t="str">
+        <v>+</v>
+      </c>
+      <c r="E18" t="str">
         <v>Permanently increase damage on use</v>
       </c>
-      <c r="E18" t="str">
+      <c r="F18" t="str">
         <v>Each time this attack is used, permanently increase its damage by X%</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>10</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -860,21 +936,24 @@
         <v>resistant</v>
       </c>
       <c r="B19" t="str">
+        <v>-</v>
+      </c>
+      <c r="C19" t="str">
         <v>Passive</v>
       </c>
-      <c r="C19" t="str">
-        <v>+</v>
-      </c>
       <c r="D19" t="str">
+        <v>+</v>
+      </c>
+      <c r="E19" t="str">
         <v>Reduce ELEMENT damage</v>
       </c>
-      <c r="E19" t="str">
+      <c r="F19" t="str">
         <v>Reduce ELEMENT damage received by X%</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>10</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -883,21 +962,24 @@
         <v>vulnerable</v>
       </c>
       <c r="B20" t="str">
+        <v>-</v>
+      </c>
+      <c r="C20" t="str">
         <v>Passive</v>
       </c>
-      <c r="C20" t="str">
+      <c r="D20" t="str">
         <v>-</v>
       </c>
-      <c r="D20" t="str">
+      <c r="E20" t="str">
         <v>Increase ELEMENT damage</v>
       </c>
-      <c r="E20" t="str">
+      <c r="F20" t="str">
         <v>Increase ELEMENT damage received by X%</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
         <v>10</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -906,21 +988,24 @@
         <v>squishy</v>
       </c>
       <c r="B21" t="str">
-        <v>Active</v>
+        <v>Fire, Earth</v>
       </c>
       <c r="C21" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D21" t="str">
         <v>-</v>
       </c>
-      <c r="D21" t="str">
-        <v>Removes X% shield</v>
-      </c>
       <c r="E21" t="str">
-        <v>Removes X% of shield from attacker when used</v>
+        <v>Removes X% of your shield on use</v>
       </c>
       <c r="F21" t="str">
+        <v>Removes X% of your shield when used</v>
+      </c>
+      <c r="G21" t="str">
         <v>100</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -929,21 +1014,24 @@
         <v>multihit</v>
       </c>
       <c r="B22" t="str">
-        <v>Active</v>
+        <v>Lightning</v>
       </c>
       <c r="C22" t="str">
-        <v>+</v>
+        <v>Active</v>
       </c>
       <c r="D22" t="str">
+        <v>+</v>
+      </c>
+      <c r="E22" t="str">
         <v>Hits multiple times</v>
       </c>
-      <c r="E22" t="str">
+      <c r="F22" t="str">
         <v>Triggers X times on use</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
         <v>2</v>
       </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>Number</v>
       </c>
     </row>
@@ -952,21 +1040,24 @@
         <v>exhaust</v>
       </c>
       <c r="B23" t="str">
-        <v>Active</v>
+        <v>Air, Water</v>
       </c>
       <c r="C23" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D23" t="str">
         <v>-</v>
       </c>
-      <c r="D23" t="str">
+      <c r="E23" t="str">
         <v>Remove X% of energy on use</v>
       </c>
-      <c r="E23" t="str">
+      <c r="F23" t="str">
         <v>Removes X% of energy when used</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
         <v>100</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -975,21 +1066,24 @@
         <v>powerful</v>
       </c>
       <c r="B24" t="str">
+        <v>Soul</v>
+      </c>
+      <c r="C24" t="str">
         <v>Creation</v>
       </c>
-      <c r="C24" t="str">
-        <v>+</v>
-      </c>
       <c r="D24" t="str">
+        <v>+</v>
+      </c>
+      <c r="E24" t="str">
         <v>Enhances damage</v>
       </c>
-      <c r="E24" t="str">
+      <c r="F24" t="str">
         <v>Increase damage by X% on creation</v>
       </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
         <v>250</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -998,21 +1092,24 @@
         <v>energetic</v>
       </c>
       <c r="B25" t="str">
+        <v>Soul</v>
+      </c>
+      <c r="C25" t="str">
         <v>Creation</v>
       </c>
-      <c r="C25" t="str">
-        <v>+</v>
-      </c>
       <c r="D25" t="str">
+        <v>+</v>
+      </c>
+      <c r="E25" t="str">
         <v>Decreases energy cost</v>
       </c>
-      <c r="E25" t="str">
+      <c r="F25" t="str">
         <v>Decrease energy cost by X on creation</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>1</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>Number</v>
       </c>
     </row>
@@ -1021,21 +1118,24 @@
         <v>efficient</v>
       </c>
       <c r="B26" t="str">
+        <v>Soul</v>
+      </c>
+      <c r="C26" t="str">
         <v>Creation</v>
       </c>
-      <c r="C26" t="str">
-        <v>+</v>
-      </c>
       <c r="D26" t="str">
+        <v>+</v>
+      </c>
+      <c r="E26" t="str">
         <v>Enhances effects</v>
       </c>
-      <c r="E26" t="str">
+      <c r="F26" t="str">
         <v>Increases value of effect by X% on creation</v>
       </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
         <v>150</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>Percent</v>
       </c>
     </row>
@@ -1044,21 +1144,24 @@
         <v>boosted</v>
       </c>
       <c r="B27" t="str">
+        <v>Air, Lightning</v>
+      </c>
+      <c r="C27" t="str">
         <v>Passive</v>
       </c>
-      <c r="C27" t="str">
-        <v>+</v>
-      </c>
       <c r="D27" t="str">
+        <v>+</v>
+      </c>
+      <c r="E27" t="str">
         <v>Increases energy at turn start</v>
       </c>
-      <c r="E27" t="str">
+      <c r="F27" t="str">
         <v>+X energy at turn start</v>
       </c>
-      <c r="F27" t="str">
+      <c r="G27" t="str">
         <v>1</v>
       </c>
-      <c r="G27" t="str">
+      <c r="H27" t="str">
         <v>Number</v>
       </c>
     </row>
@@ -1067,175 +1170,186 @@
         <v>healthy</v>
       </c>
       <c r="B28" t="str">
+        <v>Earth</v>
+      </c>
+      <c r="C28" t="str">
         <v>Passive</v>
       </c>
-      <c r="C28" t="str">
-        <v>+</v>
-      </c>
       <c r="D28" t="str">
+        <v>+</v>
+      </c>
+      <c r="E28" t="str">
         <v>Increases Max HP</v>
       </c>
-      <c r="E28" t="str">
+      <c r="F28" t="str">
         <v>+X Max HP</v>
       </c>
-      <c r="F28" t="str">
+      <c r="G28" t="str">
         <v>10</v>
       </c>
-      <c r="G28" t="str">
+      <c r="H28" t="str">
         <v>Number</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>brittle</v>
+        <v>unstable</v>
       </c>
       <c r="B29" t="str">
+        <v>Soul</v>
+      </c>
+      <c r="C29" t="str">
         <v>Element</v>
       </c>
-      <c r="C29" t="str">
-        <v>+</v>
-      </c>
       <c r="D29" t="str">
-        <v>Consumed after X uses in a FORMULA</v>
+        <v>+</v>
       </c>
       <c r="E29" t="str">
         <v>Consumed after X uses in a FORMULA</v>
       </c>
       <c r="F29" t="str">
+        <v>Consumed after X uses in a FORMULA</v>
+      </c>
+      <c r="G29" t="str">
         <v>1</v>
       </c>
-      <c r="G29" t="str">
+      <c r="H29" t="str">
         <v>Number</v>
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="str">
+        <v>gust</v>
+      </c>
       <c r="B30" t="str">
-        <v>_x000d_</v>
+        <v>Air</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D30" t="str">
+        <v>+</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Increase FIRE Damage on next attack</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Increases FIRE Damage by X% on next attack</v>
+      </c>
+      <c r="G30" t="str">
+        <v>50</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="str">
+        <v>root</v>
+      </c>
       <c r="B31" t="str">
-        <v>_x000d_</v>
+        <v>Earth</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D31" t="str">
+        <v>+</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Increase WATER Damage on next attack</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Increases WATER Damage by X% on next attack</v>
+      </c>
+      <c r="G31" t="str">
+        <v>50</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="str">
+        <v>static</v>
+      </c>
       <c r="B32" t="str">
-        <v>_x000d_</v>
+        <v>Lightning</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D32" t="str">
+        <v>+</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Increase EARTH Damage on next attack</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Increases EARTH Damage by X% on next attack</v>
+      </c>
+      <c r="G32" t="str">
+        <v>50</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="str">
+        <v>flame</v>
+      </c>
       <c r="B33" t="str">
-        <v>_x000d_</v>
+        <v>Fire</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D33" t="str">
+        <v>+</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Increase AIR Damage on next attack</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Increases AIR Damage by X% on next attack</v>
+      </c>
+      <c r="G33" t="str">
+        <v>50</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Percent</v>
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="str">
+        <v>drizzle</v>
+      </c>
       <c r="B34" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="str">
-        <v>_x000d_</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="str">
-        <v/>
+        <v>Water</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D34" t="str">
+        <v>+</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Increase LIGHTNING Damage on next attack</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Increases LIGHTNING Damage by X% on next attack</v>
+      </c>
+      <c r="G34" t="str">
+        <v>50</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Percent</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J34"/>
   </ignoredErrors>
 </worksheet>
 </file>